--- a/Analyses/2_webProbing/output/questionnaire.xlsx
+++ b/Analyses/2_webProbing/output/questionnaire.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q93"/>
+  <dimension ref="A1:T93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -440,6 +440,21 @@
           <t>feedback_critic</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>socio_sex</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>socio_age</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>socio_timeTaken</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -507,6 +522,19 @@
         <is>
           <t>No feedback other than I think the autonomy question and freedom question are very similar. I didn't mind anything. Cool study!</t>
         </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="T2">
+        <v>1733</v>
       </c>
     </row>
     <row r="3">
@@ -552,6 +580,19 @@
           <t xml:space="preserve">No, I enjoyed it. </t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="T3">
+        <v>1124</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -620,6 +661,19 @@
           <t>Great study! I enjoyed it</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="T4">
+        <v>996</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -693,6 +747,19 @@
           <t>No comment.</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>DATA_EXPIRED</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>DATA_EXPIRED</t>
+        </is>
+      </c>
+      <c r="T5">
+        <v>92257796</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -750,6 +817,19 @@
           <t>Thank you for that kind of important study.</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="T6">
+        <v>3415</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -778,6 +858,19 @@
           <t>These questions were repetitive and not easy.</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Prefer not to say</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="T7">
+        <v>1322</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -816,6 +909,19 @@
         <is>
           <t>6 - 20 - 19 - 16 - 14 - 10 - 12 - 13 - 1 - 3 - 18 - 2 - 7 - 9 - 0 - 5 - 4 - 11 - 15 - 17 - 8</t>
         </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="T8">
+        <v>1133</v>
       </c>
     </row>
     <row r="9">
@@ -872,6 +978,19 @@
           <t>14 - 18 - 12 - 6 - 17 - 1 - 8 - 7 - 16 - 10 - 4 - 19 - 20 - 3 - 5 - 13 - 15 - 9 - 0 - 11 - 2</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="T9">
+        <v>1205</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -940,6 +1059,19 @@
           <t>Redundant questions. More information needed</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="T10">
+        <v>759</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -1000,6 +1132,19 @@
           <t>The study is somewhat confusing and very repetitive.</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="T11">
+        <v>2677</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -1063,6 +1208,19 @@
           <t>7 - 18 - 13 - 11 - 5 - 9 - 16 - 6 - 12 - 17 - 15 - 14 - 10 - 2 - 19 - 20 - 3 - 0 - 8 - 4 - 1</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T12">
+        <v>1495</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -1131,6 +1289,19 @@
           <t xml:space="preserve">It did have a lot of writing, I would suggest maybe a higher payment. </t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="T13">
+        <v>983</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -1199,6 +1370,19 @@
           <t>dumb repetitive questions</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T14">
+        <v>584</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1267,6 +1451,19 @@
           <t>I wish that climate change was mentioned in the lead study text before selection.  While definitely relevant, I came here due to my love of cutting edge technology and science.  Also, ethics and morals are relative, and the answer selections should (somehow) better reflect that.  All of that said, I did thoroughly enjoy this study.  Thank you.</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="T15">
+        <v>3286</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -1327,6 +1524,19 @@
           <t>Unfortunately, I am not very knowledgeable in the field of climate engineering, but I hope my answers helped! Good luck with your study! : D</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="T16">
+        <v>2849</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1350,6 +1560,19 @@
           <t>4 - 20 - 17 - 7 - 9 - 13 - 6 - 5 - 15 - 12 - 18 - 16 - 1 - 14 - 3 - 0 - 10 - 8 - 19 - 2 - 11</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="T17">
+        <v>1042</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1381,6 +1604,19 @@
           <t>12 - 5 - 0 - 8 - 9 - 3 - 7 - 2 - 11 - 15 - 20 - 4 - 19 - 18 - 17 - 13 - 6 - 1 - 16 - 14 - 10</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="T18">
+        <v>667</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -1417,6 +1653,19 @@
           <t>5 - 6 - 16 - 13 - 8 - 15 - 4 - 18 - 10 - 12 - 19 - 17 - 7 - 9 - 11 - 14 - 3 - 0 - 20 - 2 - 1</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="T19">
+        <v>1809</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1480,6 +1729,19 @@
           <t>12 - 13 - 20 - 5 - 10 - 9 - 2 - 15 - 11 - 16 - 1 - 18 - 19 - 6 - 8 - 7 - 4 - 0 - 17 - 14 - 3</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="T20">
+        <v>624</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -1548,6 +1810,19 @@
           <t>no</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="T21">
+        <v>1307</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -1595,6 +1870,19 @@
           <t>18 - 14 - 16 - 0 - 17 - 12 - 10 - 1 - 6 - 8 - 13 - 4 - 3 - 19 - 20 - 15 - 9 - 5 - 11 - 2 - 7</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>DATA_EXPIRED</t>
+        </is>
+      </c>
+      <c r="T22">
+        <v>1851</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -1642,6 +1930,19 @@
           <t>13 - 4 - 19 - 5 - 11 - 8 - 18 - 9 - 6 - 12 - 3 - 7 - 15 - 1 - 14 - 16 - 20 - 0 - 10 - 2 - 17</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="T23">
+        <v>1398</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -1691,6 +1992,19 @@
           <t>Nothing special</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="T24">
+        <v>1868</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1759,6 +2073,19 @@
           <t>no</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="T25">
+        <v>1183</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1803,6 +2130,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="T26">
+        <v>1969</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1871,6 +2211,19 @@
           <t>No interesting topic</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="T27">
+        <v>1320</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1939,6 +2292,19 @@
           <t>Interesting study. At the beginning, with the word association game, I was unclear if you wanted single words or more complete thoughts/ideas. Good luck with your research.</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="T28">
+        <v>1466</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -2002,6 +2368,19 @@
           <t>7 - 9 - 17 - 1 - 5 - 10 - 11 - 6 - 8 - 20 - 19 - 4 - 13 - 0 - 2 - 3 - 15 - 14 - 12 - 18 - 16</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="T29">
+        <v>1307</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -2075,6 +2454,19 @@
           <t xml:space="preserve">it got a bit redundant </t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="T30">
+        <v>1893</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -2130,6 +2522,19 @@
           <t>10 - 15 - 1 - 0 - 5 - 14 - 8 - 12 - 3 - 2 - 13 - 18 - 7 - 19 - 17 - 9 - 11 - 4 - 16 - 6 - 20</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="T31">
+        <v>1502</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -2203,6 +2608,19 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="T32">
+        <v>1367</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -2247,6 +2665,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="T33">
+        <v>2719</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -2315,6 +2746,19 @@
           <t>Many of these questions were frustratingly repetitive</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="T34">
+        <v>1015</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -2388,6 +2832,19 @@
           <t>My only criticism is that some of the questions were not clear and may be confusing at times.</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="T35">
+        <v>92262309</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -2440,6 +2897,19 @@
           <t xml:space="preserve">I think that men should leave the weather business up to God. He does have a purpose for it to do as He wishes. It speaks of it in the Bible about how the weather and even the men will change towards the end of this earth age. This earth will not be renewed until the coming of Christ and after this earth is cleansed by fire. It will never be as lush as it was at the beginning of time due to mans sinful nature. I don't think that it pleases God for man to mess with His plan and weather is in the equation. </t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="T36">
+        <v>1299</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -2503,6 +2973,19 @@
           <t>20 - 11 - 12 - 3 - 2 - 1 - 17 - 15 - 9 - 8 - 0 - 5 - 16 - 14 - 4 - 18 - 6 - 19 - 7 - 10 - 13</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T37">
+        <v>1346</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -2550,6 +3033,19 @@
           <t>9 - 17 - 16 - 7 - 11 - 0 - 20 - 2 - 5 - 1 - 4 - 15 - 19 - 13 - 14 - 10 - 3 - 18 - 6 - 8 - 12</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="T38">
+        <v>1990</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -2602,6 +3098,19 @@
           <t>Thank you</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="T39">
+        <v>1977</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -2659,6 +3168,19 @@
           <t>hard concept</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="T40">
+        <v>1108</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -2727,6 +3249,19 @@
           <t>Enjoyed the study!</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="T41">
+        <v>1439</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -2800,6 +3335,19 @@
           <t>no</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T42">
+        <v>1729</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -2847,6 +3395,19 @@
           <t>12 - 1 - 2 - 16 - 6 - 5 - 14 - 20 - 15 - 9 - 11 - 10 - 13 - 8 - 18 - 0 - 17 - 19 - 4 - 3 - 7</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="T43">
+        <v>2308</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -2870,6 +3431,19 @@
           <t>13 - 15 - 6 - 17 - 3 - 8 - 19 - 1 - 20 - 0 - 9 - 5 - 14 - 7 - 2 - 10 - 11 - 16 - 18 - 4 - 12</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T44">
+        <v>1562</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -2919,6 +3493,19 @@
           <t>The pay is quite low for the amount of required writing.</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="T45">
+        <v>805</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -2966,6 +3553,19 @@
           <t>16 - 3 - 6 - 19 - 10 - 15 - 11 - 1 - 17 - 0 - 7 - 18 - 9 - 5 - 4 - 12 - 13 - 20 - 8 - 2 - 14</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="T46">
+        <v>1546</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -3029,6 +3629,19 @@
           <t>9 - 13 - 2 - 3 - 5 - 1 - 16 - 8 - 12 - 15 - 0 - 20 - 14 - 4 - 11 - 18 - 6 - 17 - 10 - 19 - 7</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="T47">
+        <v>1351</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -3097,6 +3710,19 @@
           <t>The environmentalist have a black eye in my view.  The image is tainted to my generation.  How do you prove you are no longer what has been done in the past?</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="T48">
+        <v>1834</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -3141,6 +3767,19 @@
           <t>No, it was very interesting and engaging. Thanks!</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="T49">
+        <v>1658</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -3180,6 +3819,19 @@
           <t>10 - 18 - 9 - 7 - 17 - 4 - 5 - 8 - 13 - 19 - 12 - 15 - 6 - 20 - 0 - 2 - 16 - 1 - 11 - 3 - 14</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="T50">
+        <v>1851</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -3224,6 +3876,19 @@
           <t>no</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="T51">
+        <v>1791</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -3292,6 +3957,19 @@
           <t>No</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T52">
+        <v>1665</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -3360,6 +4038,19 @@
           <t xml:space="preserve">People are going to hate stratospheric atmospheric injection, and they should. </t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="T53">
+        <v>1086</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -3399,6 +4090,19 @@
           <t>9 - 2 - 18 - 14 - 13 - 5 - 4 - 11 - 1 - 3 - 15 - 6 - 20 - 10 - 17 - 7 - 16 - 12 - 8 - 0 - 19</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="T54">
+        <v>1055</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -3443,6 +4147,19 @@
           <t>None</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="T55">
+        <v>1269</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -3495,6 +4212,19 @@
           <t>Yes.</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="T56">
+        <v>1454</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -3568,6 +4298,19 @@
           <t>thank you</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="T57">
+        <v>1954</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -3612,6 +4355,19 @@
           <t>No.</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T58">
+        <v>1266</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -3640,6 +4396,19 @@
           <t>yes the questions were hard to understand</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="T59">
+        <v>1950</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -3708,6 +4477,19 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="T60">
+        <v>1511</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -3776,6 +4558,19 @@
           <t>none</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="T61">
+        <v>1852</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -3839,6 +4634,19 @@
           <t>2 - 10 - 4 - 7 - 3 - 15 - 11 - 9 - 14 - 5 - 16 - 20 - 18 - 17 - 12 - 6 - 19 - 8 - 1 - 13 - 0</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="T62">
+        <v>1476</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -3902,6 +4710,19 @@
           <t>13 - 10 - 0 - 14 - 3 - 7 - 18 - 12 - 19 - 15 - 20 - 4 - 16 - 8 - 9 - 11 - 17 - 5 - 1 - 6 - 2</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="T63">
+        <v>775</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -3967,6 +4788,19 @@
           <t>no</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="T64">
+        <v>3230</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -4011,6 +4845,19 @@
           <t>no feedback</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="T65">
+        <v>1448</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -4079,6 +4926,19 @@
           <t>no</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="T66">
+        <v>2190</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -4147,6 +5007,19 @@
           <t xml:space="preserve">This study was excellent and certainly made me think about a subject I am extremely concerned about for the future generations.  However, hoping my answers are helpful. My brain needs a break!  </t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="T67">
+        <v>1524</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -4199,6 +5072,19 @@
           <t>no</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="T68">
+        <v>1083</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -4227,6 +5113,19 @@
           <t>If the point of this survey was to be the most annoying one ever, then congrats.....you win.</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="T69">
+        <v>1241</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -4263,6 +5162,19 @@
           <t>57d0badf28d5250001bdd9d2</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T70">
+        <v>1092</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -4331,6 +5243,19 @@
           <t>No great study</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="T71">
+        <v>1443</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -4364,6 +5289,19 @@
           <t>holy duplicate questions batman. also, both state that there is and pay more for this much writing</t>
         </is>
       </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="T72">
+        <v>966</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -4400,6 +5338,19 @@
           <t>This study was honestly very exhausting and it took me a long time. I did my best to answer the questions, but also felt pressured because a lot of the followup questions were so similar to others, and I didn't want to feel like I was giving the same answers. A little bit of clarification on some of the questions would have been extremely helpful, as I was unaware of some of the terms that were used, and had to look them up.</t>
         </is>
       </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="T73">
+        <v>2715</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -4468,6 +5419,19 @@
           <t>I like these studies do a great service to the public to show them the consequences they will face if we don't walk away from fossil fuels and greed which is killing our global existence.</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="T74">
+        <v>2069</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -4520,6 +5484,19 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="T75">
+        <v>961</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -4564,6 +5541,19 @@
           <t>10 - 16 - 11 - 9 - 17 - 18 - 6 - 4 - 3 - 12 - 1 - 7 - 15 - 14 - 13 - 20 - 5 - 8 - 2 - 19 - 0</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="T76">
+        <v>2593</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -4613,6 +5603,19 @@
           <t xml:space="preserve">i believe more would get done if democrats keep climate change about climate. Instead they turn it very political which makes it even harder to believe it, since all politicians lie. I am not sure what this study was studying but i answered everything how i felt and thought, it just happened to be political because that is how climate change is. For the record, i totally believe humans are screwing up this planet and earth would be better off without us. I just dont believe it is as serious as everyone tries to make it. Maybe in the year 2820 there may be a problem with the weather, like instead of being 85 in the summer it may be 90, just an example. There isnt really anything we humans can do to change what is going to happen. Yes we can recycle and keep the earth cleaner, but most people dont care about that, i do. </t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="T77">
+        <v>3669</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -4641,6 +5644,19 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="T78">
+        <v>1841</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -4688,6 +5704,19 @@
           <t>9 - 20 - 17 - 10 - 15 - 18 - 4 - 8 - 14 - 1 - 2 - 12 - 7 - 5 - 0 - 6 - 3 - 13 - 19 - 11 - 16</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="T79">
+        <v>2590</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -4735,6 +5764,19 @@
           <t>19 - 14 - 2 - 20 - 16 - 11 - 5 - 13 - 4 - 9 - 3 - 8 - 10 - 12 - 0 - 15 - 1 - 17 - 6 - 7 - 18</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T80">
+        <v>2283</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -4803,6 +5845,19 @@
           <t>The repeated asking of the same question is annoying, also the fullscreen, at least do dark mode.. my eyes are burning</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="T81">
+        <v>720</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -4847,6 +5902,19 @@
           <t>No issues. Great study!</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="T82">
+        <v>985</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -4910,6 +5978,19 @@
           <t>11 - 15 - 1 - 17 - 5 - 18 - 20 - 10 - 6 - 16 - 8 - 4 - 12 - 7 - 0 - 14 - 19 - 9 - 3 - 2 - 13</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="T83">
+        <v>1998</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -4962,6 +6043,19 @@
           <t>It seemed that the inquiries were very repetitive. Although it was an interesting survey. Best of luck with your research. Thank you and stay safe.</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="T84">
+        <v>2529</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -5025,6 +6119,19 @@
           <t>7 - 18 - 19 - 15 - 2 - 8 - 13 - 9 - 14 - 17 - 1 - 12 - 4 - 16 - 11 - 0 - 5 - 3 - 20 - 6 - 10</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="T85">
+        <v>1087</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -5077,6 +6184,19 @@
           <t>Your questions seem a bit vague to me? I have learning disabilities though so maybe I'm just stupid.</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="T86">
+        <v>940</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -5145,6 +6265,19 @@
           <t>I think it may have run a bit longer than the proposed 20 minutes and kept me up a little later than I intended (so perhaps indicate a higher completion time), but that might be my fault moreso for trying to provide detailed responses to be as helpful as possible. Maybe have the text available for people to re-read for review in case they didn't remember every fact of what they read. I took my time to carefully read it, so that wasn't the case in my experience. But I could see someone feeling that way. Otherwise, everything was well presented and I enjoyed my time with it. I experienced no technical issues and thank you sincerely for the opportunity to participate!</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="T87">
+        <v>2665</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -5213,6 +6346,19 @@
           <t xml:space="preserve">Nothing to add. Very interesting. </t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="T88">
+        <v>898</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -5260,6 +6406,19 @@
           <t>14 - 20 - 9 - 4 - 12 - 3 - 10 - 11 - 2 - 5 - 18 - 13 - 0 - 16 - 7 - 1 - 19 - 15 - 8 - 6 - 17</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="T89">
+        <v>1008</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -5328,6 +6487,19 @@
           <t>no</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="T90">
+        <v>1086</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -5401,6 +6573,19 @@
           <t>It's a tremendous study in which I feel excited to part of SAI technology.</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="T91">
+        <v>3458</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -5454,6 +6639,19 @@
 I also felt like more statistical data on the pros and cons might have swayed me in one direction or the other more. The statement of "takes years of treatment" was vague and had no real sense of the timeline it would take. 2 years? 3 years? 20 years? What would be the rate of temperature decline? Would it increase at first and then drop off?</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="T92">
+        <v>1368</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -5521,6 +6719,19 @@
         <is>
           <t>question wording was confusing</t>
         </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="T93">
+        <v>1039</v>
       </c>
     </row>
   </sheetData>
